--- a/base_cotizaciones_charles.xlsx
+++ b/base_cotizaciones_charles.xlsx
@@ -465,7 +465,7 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="42" customWidth="1" min="23" max="23"/>
@@ -672,11 +672,15 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Rechazada</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:08:06</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>2026-06-24 19:53:53</t>
@@ -684,7 +688,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24 19:53:53</t>
+          <t>2026-06-24 20:08:06</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -772,11 +776,15 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Vencida</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:08:15</t>
+        </is>
+      </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>2026-06-24 19:51:50</t>
@@ -784,7 +792,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24 19:51:50</t>
+          <t>2026-06-24 20:08:15</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
